--- a/Appinara_Prospekti_a_Outreach.xlsx
+++ b/Appinara_Prospekti_a_Outreach.xlsx
@@ -650,7 +650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N311"/>
+  <dimension ref="A1:N1121"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="10" min="1" max="1"/>
@@ -20375,6 +20375,23 @@
       <c r="L311" s="10" t="inlineStr">
         <is>
           <t>Apartmány+wellness+reštaurácia, 4,5/5 z 1812 Google recenzií. Aktívne tlačia priamu rezerváciu (zľava LETO26) proti OTA. Rozsiahle FAQ na webe = veľa opakovaných otázok. Recenzie chvália kuchyňu, drobné sťažnosti na upratovanie. EMAIL NEZOBRAZENÝ - overiť. Tón: rodinný, férové ceny.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="K1121" t="inlineStr">
+        <is>
+          <t>Odoslané</t>
+        </is>
+      </c>
+      <c r="L1121" t="inlineStr">
+        <is>
+          <t>25.09.2026</t>
+        </is>
+      </c>
+      <c r="N1121" t="inlineStr">
+        <is>
+          <t>25.09.2026</t>
         </is>
       </c>
     </row>
